--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -759,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="12.5703125" customWidth="1" style="13" min="1" max="1"/>
@@ -770,13 +770,9 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45173.57052414889</v>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
+        <v>45216</v>
+      </c>
+    </row>
     <row r="6" ht="22.5" customHeight="1" s="13">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -799,8 +795,6 @@
       </c>
       <c r="E8" s="16" t="n"/>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="13">
       <c r="A11" s="14" t="inlineStr">
         <is>
@@ -811,17 +805,6 @@
     <row r="12" ht="41.25" customHeight="1" s="13">
       <c r="A12" s="15" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
     <row r="24" ht="33.75" customHeight="1" s="13">
       <c r="B24" s="12" t="inlineStr">
         <is>
@@ -829,8 +812,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27" ht="18" customHeight="1" s="13">
       <c r="A27" s="4" t="inlineStr">
         <is>
@@ -861,8 +842,10 @@
         </is>
       </c>
       <c r="C28" s="20" t="n"/>
-      <c r="D28" s="11" t="n">
-        <v>451.425</v>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>469.482</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="18" customFormat="1" customHeight="1" s="7">
@@ -877,8 +860,10 @@
         </is>
       </c>
       <c r="C29" s="20" t="n"/>
-      <c r="D29" s="11" t="n">
-        <v>515.917</v>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>536.554</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="18" customFormat="1" customHeight="1" s="7">
@@ -893,8 +878,10 @@
         </is>
       </c>
       <c r="C30" s="20" t="n"/>
-      <c r="D30" s="11" t="n">
-        <v>590.3819999999999</v>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>613.997</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="18" customFormat="1" customHeight="1" s="7">
@@ -909,8 +896,10 @@
         </is>
       </c>
       <c r="C31" s="20" t="n"/>
-      <c r="D31" s="11" t="n">
-        <v>690.645</v>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>718.271</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="18" customFormat="1" customHeight="1" s="7">
@@ -925,8 +914,10 @@
         </is>
       </c>
       <c r="C32" s="20" t="n"/>
-      <c r="D32" s="11" t="n">
-        <v>755.622</v>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>785.847</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="18" customFormat="1" customHeight="1" s="7">
@@ -941,8 +932,10 @@
         </is>
       </c>
       <c r="C33" s="20" t="n"/>
-      <c r="D33" s="11" t="n">
-        <v>900.421</v>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>936.438</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="18" customFormat="1" customHeight="1" s="7">
@@ -957,8 +950,10 @@
         </is>
       </c>
       <c r="C34" s="20" t="n"/>
-      <c r="D34" s="11" t="n">
-        <v>922.3200000000001</v>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>959.213</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="18" customFormat="1" customHeight="1" s="7">
@@ -973,8 +968,10 @@
         </is>
       </c>
       <c r="C35" s="20" t="n"/>
-      <c r="D35" s="11" t="n">
-        <v>1028.91</v>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>1070.066</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="18" customFormat="1" customHeight="1" s="7">
@@ -989,8 +986,10 @@
         </is>
       </c>
       <c r="C36" s="20" t="n"/>
-      <c r="D36" s="11" t="n">
-        <v>1245.983</v>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>1295.822</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1005,8 +1004,10 @@
         </is>
       </c>
       <c r="C37" s="20" t="n"/>
-      <c r="D37" s="11" t="n">
-        <v>1406.6</v>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>1462.864</t>
+        </is>
       </c>
     </row>
     <row r="38" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1021,8 +1022,10 @@
         </is>
       </c>
       <c r="C38" s="20" t="n"/>
-      <c r="D38" s="11" t="n">
-        <v>1642.655</v>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>1708.361</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1037,8 +1040,10 @@
         </is>
       </c>
       <c r="C39" s="20" t="n"/>
-      <c r="D39" s="11" t="n">
-        <v>1813.006</v>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>1885.526</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1053,8 +1058,10 @@
         </is>
       </c>
       <c r="C40" s="20" t="n"/>
-      <c r="D40" s="11" t="n">
-        <v>1971.187</v>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>2050.034</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1069,8 +1076,10 @@
         </is>
       </c>
       <c r="C41" s="20" t="n"/>
-      <c r="D41" s="11" t="n">
-        <v>2214.542</v>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>2303.124</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1085,8 +1094,10 @@
         </is>
       </c>
       <c r="C42" s="20" t="n"/>
-      <c r="D42" s="11" t="n">
-        <v>2362.989</v>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>2457.509</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1101,8 +1112,10 @@
         </is>
       </c>
       <c r="C43" s="20" t="n"/>
-      <c r="D43" s="11" t="n">
-        <v>2577.143</v>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>2680.229</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="13"/>
@@ -1148,8 +1161,10 @@
         </is>
       </c>
       <c r="C49" s="20" t="n"/>
-      <c r="D49" s="11" t="n">
-        <v>1447.971</v>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>1505.89</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1" s="13">
@@ -1164,8 +1179,10 @@
         </is>
       </c>
       <c r="C50" s="20" t="n"/>
-      <c r="D50" s="11" t="n">
-        <v>1455.271</v>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>1513.482</t>
+        </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1" s="13">
@@ -1180,8 +1197,10 @@
         </is>
       </c>
       <c r="C51" s="20" t="n"/>
-      <c r="D51" s="11" t="n">
-        <v>1786.235</v>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>1857.684</t>
+        </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1" s="13">
@@ -1196,8 +1215,10 @@
         </is>
       </c>
       <c r="C52" s="20" t="n"/>
-      <c r="D52" s="11" t="n">
-        <v>1910.349</v>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>1986.763</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" s="13">
@@ -1212,8 +1233,10 @@
         </is>
       </c>
       <c r="C53" s="20" t="n"/>
-      <c r="D53" s="11" t="n">
-        <v>2034.698</v>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>2116.086</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" s="13">
@@ -1228,8 +1251,10 @@
         </is>
       </c>
       <c r="C54" s="20" t="n"/>
-      <c r="D54" s="11" t="n">
-        <v>2289.981</v>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>2381.58</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" s="13">
@@ -1244,8 +1269,10 @@
         </is>
       </c>
       <c r="C55" s="20" t="n"/>
-      <c r="D55" s="11" t="n">
-        <v>2664.75</v>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>2771.34</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" s="13">
@@ -1260,8 +1287,10 @@
         </is>
       </c>
       <c r="C56" s="20" t="n"/>
-      <c r="D56" s="11" t="n">
-        <v>2983.547</v>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>3102.889</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1" s="13">
@@ -1276,8 +1305,10 @@
         </is>
       </c>
       <c r="C57" s="20" t="n"/>
-      <c r="D57" s="11" t="n">
-        <v>3411.853</v>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>3548.327</t>
+        </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" s="13">
@@ -1292,8 +1323,10 @@
         </is>
       </c>
       <c r="C58" s="20" t="n"/>
-      <c r="D58" s="11" t="n">
-        <v>3845.027</v>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>3998.828</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" s="13">
@@ -1308,8 +1341,10 @@
         </is>
       </c>
       <c r="C59" s="20" t="n"/>
-      <c r="D59" s="11" t="n">
-        <v>4173.555</v>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>4340.497</t>
+        </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1" s="13">
@@ -1324,8 +1359,10 @@
         </is>
       </c>
       <c r="C60" s="20" t="n"/>
-      <c r="D60" s="11" t="n">
-        <v>4696.773</v>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>4884.644</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1" s="13">
@@ -1340,8 +1377,10 @@
         </is>
       </c>
       <c r="C61" s="20" t="n"/>
-      <c r="D61" s="11" t="n">
-        <v>5181.049</v>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>5388.291</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1" s="13">
@@ -1356,12 +1395,12 @@
         </is>
       </c>
       <c r="C62" s="20" t="n"/>
-      <c r="D62" s="11" t="n">
-        <v>5487.677</v>
-      </c>
-    </row>
-    <row r="63"/>
-    <row r="64"/>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>5707.184</t>
+        </is>
+      </c>
+    </row>
     <row r="65" ht="33.75" customHeight="1" s="13">
       <c r="B65" s="12" t="inlineStr">
         <is>
@@ -1403,8 +1442,10 @@
         </is>
       </c>
       <c r="C68" s="20" t="n"/>
-      <c r="D68" s="11" t="n">
-        <v>584.299</v>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>607.671</t>
+        </is>
       </c>
     </row>
     <row r="69" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1419,8 +1460,10 @@
         </is>
       </c>
       <c r="C69" s="20" t="n"/>
-      <c r="D69" s="11" t="n">
-        <v>601.09</v>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>625.134</t>
+        </is>
       </c>
     </row>
     <row r="70" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1435,8 +1478,10 @@
         </is>
       </c>
       <c r="C70" s="20" t="n"/>
-      <c r="D70" s="11" t="n">
-        <v>680.181</v>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>707.388</t>
+        </is>
       </c>
     </row>
     <row r="71" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1451,8 +1496,10 @@
         </is>
       </c>
       <c r="C71" s="20" t="n"/>
-      <c r="D71" s="11" t="n">
-        <v>792.369</v>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>824.064</t>
+        </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1" s="13">
@@ -1467,8 +1514,10 @@
         </is>
       </c>
       <c r="C72" s="20" t="n"/>
-      <c r="D72" s="11" t="n">
-        <v>916.482</v>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>953.141</t>
+        </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="13">
@@ -1483,8 +1532,10 @@
         </is>
       </c>
       <c r="C73" s="20" t="n"/>
-      <c r="D73" s="11" t="n">
-        <v>1062.493</v>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>1104.993</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1" s="13">
@@ -1499,8 +1550,10 @@
         </is>
       </c>
       <c r="C74" s="20" t="n"/>
-      <c r="D74" s="11" t="n">
-        <v>1190.012</v>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>1237.612</t>
+        </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="13">
@@ -1515,8 +1568,10 @@
         </is>
       </c>
       <c r="C75" s="20" t="n"/>
-      <c r="D75" s="11" t="n">
-        <v>1260.585</v>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>1311.008</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" s="13">
@@ -1531,8 +1586,10 @@
         </is>
       </c>
       <c r="C76" s="20" t="n"/>
-      <c r="D76" s="11" t="n">
-        <v>1484.471</v>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>1543.85</t>
+        </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1" s="13">
@@ -1547,8 +1604,10 @@
         </is>
       </c>
       <c r="C77" s="20" t="n"/>
-      <c r="D77" s="11" t="n">
-        <v>1720.53</v>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>1789.351</t>
+        </is>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1" s="13">
@@ -1563,8 +1622,10 @@
         </is>
       </c>
       <c r="C78" s="20" t="n"/>
-      <c r="D78" s="11" t="n">
-        <v>1916.915</v>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>1993.592</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1" s="13">
@@ -1579,8 +1640,10 @@
         </is>
       </c>
       <c r="C79" s="20" t="n"/>
-      <c r="D79" s="11" t="n">
-        <v>2148.346</v>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>2234.28</t>
+        </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1" s="13">
@@ -1595,8 +1658,10 @@
         </is>
       </c>
       <c r="C80" s="20" t="n"/>
-      <c r="D80" s="11" t="n">
-        <v>2397.06</v>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>2492.942</t>
+        </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1" s="13">
@@ -1611,8 +1676,10 @@
         </is>
       </c>
       <c r="C81" s="20" t="n"/>
-      <c r="D81" s="11" t="n">
-        <v>2538.933</v>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>2640.49</t>
+        </is>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1" s="13">
@@ -1627,8 +1694,10 @@
         </is>
       </c>
       <c r="C82" s="20" t="n"/>
-      <c r="D82" s="11" t="n">
-        <v>2752.359</v>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>2862.453</t>
+        </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1" s="13">
@@ -1643,12 +1712,12 @@
         </is>
       </c>
       <c r="C83" s="20" t="n"/>
-      <c r="D83" s="11" t="n">
-        <v>3005.447</v>
-      </c>
-    </row>
-    <row r="84"/>
-    <row r="85"/>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>3125.665</t>
+        </is>
+      </c>
+    </row>
     <row r="86" ht="33.75" customHeight="1" s="13">
       <c r="B86" s="12" t="inlineStr">
         <is>
@@ -1656,7 +1725,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
     <row r="88" ht="18" customHeight="1" s="13">
       <c r="A88" s="4" t="inlineStr">
         <is>
@@ -1687,8 +1755,10 @@
         </is>
       </c>
       <c r="C89" s="20" t="n"/>
-      <c r="D89" s="11" t="n">
-        <v>249.883</v>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>259.878</t>
+        </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1" s="13">
@@ -1703,8 +1773,10 @@
         </is>
       </c>
       <c r="C90" s="20" t="n"/>
-      <c r="D90" s="11" t="n">
-        <v>300.06</v>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>312.062</t>
+        </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1" s="13">
@@ -1719,8 +1791,10 @@
         </is>
       </c>
       <c r="C91" s="20" t="n"/>
-      <c r="D91" s="11" t="n">
-        <v>324.394</v>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>337.37</t>
+        </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1" s="13">
@@ -1735,8 +1809,10 @@
         </is>
       </c>
       <c r="C92" s="20" t="n"/>
-      <c r="D92" s="11" t="n">
-        <v>402.51</v>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>418.61</t>
+        </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1" s="13">
@@ -1751,8 +1827,10 @@
         </is>
       </c>
       <c r="C93" s="20" t="n"/>
-      <c r="D93" s="11" t="n">
-        <v>439.257</v>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>456.827</t>
+        </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1" s="13">
@@ -1767,8 +1845,10 @@
         </is>
       </c>
       <c r="C94" s="20" t="n"/>
-      <c r="D94" s="11" t="n">
-        <v>473.085</v>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>492.008</t>
+        </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1" s="13">
@@ -1783,8 +1863,10 @@
         </is>
       </c>
       <c r="C95" s="20" t="n"/>
-      <c r="D95" s="11" t="n">
-        <v>519.079</v>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>539.842</t>
+        </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1" s="13">
@@ -1799,8 +1881,10 @@
         </is>
       </c>
       <c r="C96" s="20" t="n"/>
-      <c r="D96" s="11" t="n">
-        <v>662.4160000000001</v>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>688.913</t>
+        </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1" s="13">
@@ -1815,8 +1899,10 @@
         </is>
       </c>
       <c r="C97" s="20" t="n"/>
-      <c r="D97" s="11" t="n">
-        <v>720.333</v>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>749.146</t>
+        </is>
       </c>
     </row>
     <row r="98" ht="19.5" customHeight="1" s="13">
@@ -1831,8 +1917,10 @@
         </is>
       </c>
       <c r="C98" s="20" t="n"/>
-      <c r="D98" s="11" t="n">
-        <v>844.4450000000001</v>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>878.223</t>
+        </is>
       </c>
     </row>
     <row r="99" ht="17.25" customHeight="1" s="13">
@@ -1847,8 +1935,10 @@
         </is>
       </c>
       <c r="C99" s="20" t="n"/>
-      <c r="D99" s="11" t="n">
-        <v>953.956</v>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>992.114</t>
+        </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1" s="13">
@@ -1863,12 +1953,12 @@
         </is>
       </c>
       <c r="C100" s="20" t="n"/>
-      <c r="D100" s="11" t="n">
-        <v>1026.963</v>
-      </c>
-    </row>
-    <row r="101"/>
-    <row r="102"/>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>1068.042</t>
+        </is>
+      </c>
+    </row>
     <row r="103" ht="33.75" customHeight="1" s="13">
       <c r="B103" s="12" t="inlineStr">
         <is>
@@ -1876,7 +1966,6 @@
         </is>
       </c>
     </row>
-    <row r="104"/>
     <row r="105" ht="18" customHeight="1" s="13">
       <c r="A105" s="4" t="inlineStr">
         <is>
@@ -1907,8 +1996,10 @@
         </is>
       </c>
       <c r="C106" s="20" t="n"/>
-      <c r="D106" s="11" t="n">
-        <v>2314.315</v>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>2406.888</t>
+        </is>
       </c>
     </row>
     <row r="107" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1923,8 +2014,10 @@
         </is>
       </c>
       <c r="C107" s="20" t="n"/>
-      <c r="D107" s="11" t="n">
-        <v>2460.331</v>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>2558.744</t>
+        </is>
       </c>
     </row>
     <row r="108" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1939,8 +2032,10 @@
         </is>
       </c>
       <c r="C108" s="20" t="n"/>
-      <c r="D108" s="11" t="n">
-        <v>2603.912</v>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>2708.068</t>
+        </is>
       </c>
     </row>
     <row r="109" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1955,8 +2050,10 @@
         </is>
       </c>
       <c r="C109" s="20" t="n"/>
-      <c r="D109" s="11" t="n">
-        <v>2847.269</v>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>2961.16</t>
+        </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1" s="13">
@@ -1971,8 +2068,10 @@
         </is>
       </c>
       <c r="C110" s="20" t="n"/>
-      <c r="D110" s="11" t="n">
-        <v>2864.303</v>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>2978.875</t>
+        </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1" s="13">
@@ -1987,8 +2086,10 @@
         </is>
       </c>
       <c r="C111" s="20" t="n"/>
-      <c r="D111" s="11" t="n">
-        <v>3375.35</v>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>3510.364</t>
+        </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1" s="13">
@@ -2003,8 +2104,10 @@
         </is>
       </c>
       <c r="C112" s="20" t="n"/>
-      <c r="D112" s="11" t="n">
-        <v>3995.906</v>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>4155.742</t>
+        </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1" s="13">
@@ -2019,8 +2122,10 @@
         </is>
       </c>
       <c r="C113" s="20" t="n"/>
-      <c r="D113" s="11" t="n">
-        <v>4429.082</v>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>4606.245</t>
+        </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1" s="13">
@@ -2035,8 +2140,10 @@
         </is>
       </c>
       <c r="C114" s="20" t="n"/>
-      <c r="D114" s="11" t="n">
-        <v>4842.789</v>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>5036.501</t>
+        </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1" s="13">
@@ -2051,8 +2158,10 @@
         </is>
       </c>
       <c r="C115" s="20" t="n"/>
-      <c r="D115" s="11" t="n">
-        <v>5346.536</v>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>5560.397</t>
+        </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1" s="13">
@@ -2067,8 +2176,10 @@
         </is>
       </c>
       <c r="C116" s="20" t="n"/>
-      <c r="D116" s="11" t="n">
-        <v>5986.559</v>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>6226.021</t>
+        </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1" s="13">
@@ -2083,8 +2194,10 @@
         </is>
       </c>
       <c r="C117" s="20" t="n"/>
-      <c r="D117" s="11" t="n">
-        <v>6324.827</v>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>6577.82</t>
+        </is>
       </c>
     </row>
     <row r="118" ht="19.5" customHeight="1" s="13">
@@ -2099,8 +2212,10 @@
         </is>
       </c>
       <c r="C118" s="20" t="n"/>
-      <c r="D118" s="11" t="n">
-        <v>7057.326</v>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>7339.619</t>
+        </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1" s="13">
@@ -2115,91 +2230,92 @@
         </is>
       </c>
       <c r="C119" s="20" t="n"/>
-      <c r="D119" s="11" t="n">
-        <v>7483.2</v>
-      </c>
-    </row>
-    <row r="120"/>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>7782.528</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B51:C51"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B92:C92"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B59:C59"/>
     <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B70:C70"/>
     <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B111:C111"/>
     <mergeCell ref="B73:C73"/>
     <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B110:C110"/>
     <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B110:C110"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45216</v>
+        <v>45217</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">

--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45217</v>
+        <v>45219</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">
@@ -842,10 +842,8 @@
         </is>
       </c>
       <c r="C28" s="20" t="n"/>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>469.482</t>
-        </is>
+      <c r="D28" s="11" t="n">
+        <v>469.482</v>
       </c>
     </row>
     <row r="29" ht="18" customFormat="1" customHeight="1" s="7">
@@ -860,10 +858,8 @@
         </is>
       </c>
       <c r="C29" s="20" t="n"/>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>536.554</t>
-        </is>
+      <c r="D29" s="11" t="n">
+        <v>536.554</v>
       </c>
     </row>
     <row r="30" ht="18" customFormat="1" customHeight="1" s="7">
@@ -878,10 +874,8 @@
         </is>
       </c>
       <c r="C30" s="20" t="n"/>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>613.997</t>
-        </is>
+      <c r="D30" s="11" t="n">
+        <v>613.997</v>
       </c>
     </row>
     <row r="31" ht="18" customFormat="1" customHeight="1" s="7">
@@ -896,10 +890,8 @@
         </is>
       </c>
       <c r="C31" s="20" t="n"/>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>718.271</t>
-        </is>
+      <c r="D31" s="11" t="n">
+        <v>718.271</v>
       </c>
     </row>
     <row r="32" ht="18" customFormat="1" customHeight="1" s="7">
@@ -914,10 +906,8 @@
         </is>
       </c>
       <c r="C32" s="20" t="n"/>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>785.847</t>
-        </is>
+      <c r="D32" s="11" t="n">
+        <v>785.847</v>
       </c>
     </row>
     <row r="33" ht="18" customFormat="1" customHeight="1" s="7">
@@ -932,10 +922,8 @@
         </is>
       </c>
       <c r="C33" s="20" t="n"/>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>936.438</t>
-        </is>
+      <c r="D33" s="11" t="n">
+        <v>936.438</v>
       </c>
     </row>
     <row r="34" ht="18" customFormat="1" customHeight="1" s="7">
@@ -950,10 +938,8 @@
         </is>
       </c>
       <c r="C34" s="20" t="n"/>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>959.213</t>
-        </is>
+      <c r="D34" s="11" t="n">
+        <v>959.213</v>
       </c>
     </row>
     <row r="35" ht="18" customFormat="1" customHeight="1" s="7">
@@ -968,10 +954,8 @@
         </is>
       </c>
       <c r="C35" s="20" t="n"/>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>1070.066</t>
-        </is>
+      <c r="D35" s="11" t="n">
+        <v>1070.066</v>
       </c>
     </row>
     <row r="36" ht="18" customFormat="1" customHeight="1" s="7">
@@ -986,10 +970,8 @@
         </is>
       </c>
       <c r="C36" s="20" t="n"/>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>1295.822</t>
-        </is>
+      <c r="D36" s="11" t="n">
+        <v>1295.822</v>
       </c>
     </row>
     <row r="37" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1004,10 +986,8 @@
         </is>
       </c>
       <c r="C37" s="20" t="n"/>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>1462.864</t>
-        </is>
+      <c r="D37" s="11" t="n">
+        <v>1462.864</v>
       </c>
     </row>
     <row r="38" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1022,10 +1002,8 @@
         </is>
       </c>
       <c r="C38" s="20" t="n"/>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>1708.361</t>
-        </is>
+      <c r="D38" s="11" t="n">
+        <v>1708.361</v>
       </c>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1040,10 +1018,8 @@
         </is>
       </c>
       <c r="C39" s="20" t="n"/>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>1885.526</t>
-        </is>
+      <c r="D39" s="11" t="n">
+        <v>1885.526</v>
       </c>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1058,10 +1034,8 @@
         </is>
       </c>
       <c r="C40" s="20" t="n"/>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>2050.034</t>
-        </is>
+      <c r="D40" s="11" t="n">
+        <v>2050.034</v>
       </c>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1076,10 +1050,8 @@
         </is>
       </c>
       <c r="C41" s="20" t="n"/>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>2303.124</t>
-        </is>
+      <c r="D41" s="11" t="n">
+        <v>2303.124</v>
       </c>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1094,10 +1066,8 @@
         </is>
       </c>
       <c r="C42" s="20" t="n"/>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>2457.509</t>
-        </is>
+      <c r="D42" s="11" t="n">
+        <v>2457.509</v>
       </c>
     </row>
     <row r="43" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1112,10 +1082,8 @@
         </is>
       </c>
       <c r="C43" s="20" t="n"/>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>2680.229</t>
-        </is>
+      <c r="D43" s="11" t="n">
+        <v>2680.229</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="13"/>
@@ -1161,10 +1129,8 @@
         </is>
       </c>
       <c r="C49" s="20" t="n"/>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>1505.89</t>
-        </is>
+      <c r="D49" s="11" t="n">
+        <v>1505.89</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1" s="13">
@@ -1179,10 +1145,8 @@
         </is>
       </c>
       <c r="C50" s="20" t="n"/>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>1513.482</t>
-        </is>
+      <c r="D50" s="11" t="n">
+        <v>1513.482</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1" s="13">
@@ -1197,10 +1161,8 @@
         </is>
       </c>
       <c r="C51" s="20" t="n"/>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>1857.684</t>
-        </is>
+      <c r="D51" s="11" t="n">
+        <v>1857.684</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1" s="13">
@@ -1215,10 +1177,8 @@
         </is>
       </c>
       <c r="C52" s="20" t="n"/>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>1986.763</t>
-        </is>
+      <c r="D52" s="11" t="n">
+        <v>1986.763</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" s="13">
@@ -1233,10 +1193,8 @@
         </is>
       </c>
       <c r="C53" s="20" t="n"/>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>2116.086</t>
-        </is>
+      <c r="D53" s="11" t="n">
+        <v>2116.086</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" s="13">
@@ -1251,10 +1209,8 @@
         </is>
       </c>
       <c r="C54" s="20" t="n"/>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>2381.58</t>
-        </is>
+      <c r="D54" s="11" t="n">
+        <v>2381.58</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" s="13">
@@ -1269,10 +1225,8 @@
         </is>
       </c>
       <c r="C55" s="20" t="n"/>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>2771.34</t>
-        </is>
+      <c r="D55" s="11" t="n">
+        <v>2771.34</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" s="13">
@@ -1287,10 +1241,8 @@
         </is>
       </c>
       <c r="C56" s="20" t="n"/>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>3102.889</t>
-        </is>
+      <c r="D56" s="11" t="n">
+        <v>3102.889</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1" s="13">
@@ -1305,10 +1257,8 @@
         </is>
       </c>
       <c r="C57" s="20" t="n"/>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>3548.327</t>
-        </is>
+      <c r="D57" s="11" t="n">
+        <v>3548.327</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" s="13">
@@ -1323,10 +1273,8 @@
         </is>
       </c>
       <c r="C58" s="20" t="n"/>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>3998.828</t>
-        </is>
+      <c r="D58" s="11" t="n">
+        <v>3998.828</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" s="13">
@@ -1341,10 +1289,8 @@
         </is>
       </c>
       <c r="C59" s="20" t="n"/>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>4340.497</t>
-        </is>
+      <c r="D59" s="11" t="n">
+        <v>4340.497</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1" s="13">
@@ -1359,10 +1305,8 @@
         </is>
       </c>
       <c r="C60" s="20" t="n"/>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>4884.644</t>
-        </is>
+      <c r="D60" s="11" t="n">
+        <v>4884.644</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1" s="13">
@@ -1377,10 +1321,8 @@
         </is>
       </c>
       <c r="C61" s="20" t="n"/>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>5388.291</t>
-        </is>
+      <c r="D61" s="11" t="n">
+        <v>5388.291</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1" s="13">
@@ -1395,10 +1337,8 @@
         </is>
       </c>
       <c r="C62" s="20" t="n"/>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>5707.184</t>
-        </is>
+      <c r="D62" s="11" t="n">
+        <v>5707.184</v>
       </c>
     </row>
     <row r="65" ht="33.75" customHeight="1" s="13">
@@ -1442,10 +1382,8 @@
         </is>
       </c>
       <c r="C68" s="20" t="n"/>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>607.671</t>
-        </is>
+      <c r="D68" s="11" t="n">
+        <v>607.671</v>
       </c>
     </row>
     <row r="69" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1460,10 +1398,8 @@
         </is>
       </c>
       <c r="C69" s="20" t="n"/>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>625.134</t>
-        </is>
+      <c r="D69" s="11" t="n">
+        <v>625.134</v>
       </c>
     </row>
     <row r="70" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1478,10 +1414,8 @@
         </is>
       </c>
       <c r="C70" s="20" t="n"/>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>707.388</t>
-        </is>
+      <c r="D70" s="11" t="n">
+        <v>707.388</v>
       </c>
     </row>
     <row r="71" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1496,10 +1430,8 @@
         </is>
       </c>
       <c r="C71" s="20" t="n"/>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>824.064</t>
-        </is>
+      <c r="D71" s="11" t="n">
+        <v>824.064</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1" s="13">
@@ -1514,10 +1446,8 @@
         </is>
       </c>
       <c r="C72" s="20" t="n"/>
-      <c r="D72" s="11" t="inlineStr">
-        <is>
-          <t>953.141</t>
-        </is>
+      <c r="D72" s="11" t="n">
+        <v>953.141</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="13">
@@ -1532,10 +1462,8 @@
         </is>
       </c>
       <c r="C73" s="20" t="n"/>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>1104.993</t>
-        </is>
+      <c r="D73" s="11" t="n">
+        <v>1104.993</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1" s="13">
@@ -1550,10 +1478,8 @@
         </is>
       </c>
       <c r="C74" s="20" t="n"/>
-      <c r="D74" s="11" t="inlineStr">
-        <is>
-          <t>1237.612</t>
-        </is>
+      <c r="D74" s="11" t="n">
+        <v>1237.612</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="13">
@@ -1568,10 +1494,8 @@
         </is>
       </c>
       <c r="C75" s="20" t="n"/>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>1311.008</t>
-        </is>
+      <c r="D75" s="11" t="n">
+        <v>1311.008</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" s="13">
@@ -1586,10 +1510,8 @@
         </is>
       </c>
       <c r="C76" s="20" t="n"/>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>1543.85</t>
-        </is>
+      <c r="D76" s="11" t="n">
+        <v>1543.85</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1" s="13">
@@ -1604,10 +1526,8 @@
         </is>
       </c>
       <c r="C77" s="20" t="n"/>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>1789.351</t>
-        </is>
+      <c r="D77" s="11" t="n">
+        <v>1789.351</v>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1" s="13">
@@ -1622,10 +1542,8 @@
         </is>
       </c>
       <c r="C78" s="20" t="n"/>
-      <c r="D78" s="11" t="inlineStr">
-        <is>
-          <t>1993.592</t>
-        </is>
+      <c r="D78" s="11" t="n">
+        <v>1993.592</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1" s="13">
@@ -1640,10 +1558,8 @@
         </is>
       </c>
       <c r="C79" s="20" t="n"/>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>2234.28</t>
-        </is>
+      <c r="D79" s="11" t="n">
+        <v>2234.28</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1" s="13">
@@ -1658,10 +1574,8 @@
         </is>
       </c>
       <c r="C80" s="20" t="n"/>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>2492.942</t>
-        </is>
+      <c r="D80" s="11" t="n">
+        <v>2492.942</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1" s="13">
@@ -1676,10 +1590,8 @@
         </is>
       </c>
       <c r="C81" s="20" t="n"/>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>2640.49</t>
-        </is>
+      <c r="D81" s="11" t="n">
+        <v>2640.49</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1" s="13">
@@ -1694,10 +1606,8 @@
         </is>
       </c>
       <c r="C82" s="20" t="n"/>
-      <c r="D82" s="11" t="inlineStr">
-        <is>
-          <t>2862.453</t>
-        </is>
+      <c r="D82" s="11" t="n">
+        <v>2862.453</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1" s="13">
@@ -1712,10 +1622,8 @@
         </is>
       </c>
       <c r="C83" s="20" t="n"/>
-      <c r="D83" s="11" t="inlineStr">
-        <is>
-          <t>3125.665</t>
-        </is>
+      <c r="D83" s="11" t="n">
+        <v>3125.665</v>
       </c>
     </row>
     <row r="86" ht="33.75" customHeight="1" s="13">
@@ -1755,10 +1663,8 @@
         </is>
       </c>
       <c r="C89" s="20" t="n"/>
-      <c r="D89" s="11" t="inlineStr">
-        <is>
-          <t>259.878</t>
-        </is>
+      <c r="D89" s="11" t="n">
+        <v>259.878</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1" s="13">
@@ -1773,10 +1679,8 @@
         </is>
       </c>
       <c r="C90" s="20" t="n"/>
-      <c r="D90" s="11" t="inlineStr">
-        <is>
-          <t>312.062</t>
-        </is>
+      <c r="D90" s="11" t="n">
+        <v>312.062</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1" s="13">
@@ -1791,10 +1695,8 @@
         </is>
       </c>
       <c r="C91" s="20" t="n"/>
-      <c r="D91" s="11" t="inlineStr">
-        <is>
-          <t>337.37</t>
-        </is>
+      <c r="D91" s="11" t="n">
+        <v>337.37</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1" s="13">
@@ -1809,10 +1711,8 @@
         </is>
       </c>
       <c r="C92" s="20" t="n"/>
-      <c r="D92" s="11" t="inlineStr">
-        <is>
-          <t>418.61</t>
-        </is>
+      <c r="D92" s="11" t="n">
+        <v>418.61</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1" s="13">
@@ -1827,10 +1727,8 @@
         </is>
       </c>
       <c r="C93" s="20" t="n"/>
-      <c r="D93" s="11" t="inlineStr">
-        <is>
-          <t>456.827</t>
-        </is>
+      <c r="D93" s="11" t="n">
+        <v>456.827</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1" s="13">
@@ -1845,10 +1743,8 @@
         </is>
       </c>
       <c r="C94" s="20" t="n"/>
-      <c r="D94" s="11" t="inlineStr">
-        <is>
-          <t>492.008</t>
-        </is>
+      <c r="D94" s="11" t="n">
+        <v>492.008</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1" s="13">
@@ -1863,10 +1759,8 @@
         </is>
       </c>
       <c r="C95" s="20" t="n"/>
-      <c r="D95" s="11" t="inlineStr">
-        <is>
-          <t>539.842</t>
-        </is>
+      <c r="D95" s="11" t="n">
+        <v>539.842</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1" s="13">
@@ -1881,10 +1775,8 @@
         </is>
       </c>
       <c r="C96" s="20" t="n"/>
-      <c r="D96" s="11" t="inlineStr">
-        <is>
-          <t>688.913</t>
-        </is>
+      <c r="D96" s="11" t="n">
+        <v>688.913</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1" s="13">
@@ -1899,10 +1791,8 @@
         </is>
       </c>
       <c r="C97" s="20" t="n"/>
-      <c r="D97" s="11" t="inlineStr">
-        <is>
-          <t>749.146</t>
-        </is>
+      <c r="D97" s="11" t="n">
+        <v>749.146</v>
       </c>
     </row>
     <row r="98" ht="19.5" customHeight="1" s="13">
@@ -1917,10 +1807,8 @@
         </is>
       </c>
       <c r="C98" s="20" t="n"/>
-      <c r="D98" s="11" t="inlineStr">
-        <is>
-          <t>878.223</t>
-        </is>
+      <c r="D98" s="11" t="n">
+        <v>878.223</v>
       </c>
     </row>
     <row r="99" ht="17.25" customHeight="1" s="13">
@@ -1935,10 +1823,8 @@
         </is>
       </c>
       <c r="C99" s="20" t="n"/>
-      <c r="D99" s="11" t="inlineStr">
-        <is>
-          <t>992.114</t>
-        </is>
+      <c r="D99" s="11" t="n">
+        <v>992.114</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1" s="13">
@@ -1953,10 +1839,8 @@
         </is>
       </c>
       <c r="C100" s="20" t="n"/>
-      <c r="D100" s="11" t="inlineStr">
-        <is>
-          <t>1068.042</t>
-        </is>
+      <c r="D100" s="11" t="n">
+        <v>1068.042</v>
       </c>
     </row>
     <row r="103" ht="33.75" customHeight="1" s="13">
@@ -1996,10 +1880,8 @@
         </is>
       </c>
       <c r="C106" s="20" t="n"/>
-      <c r="D106" s="11" t="inlineStr">
-        <is>
-          <t>2406.888</t>
-        </is>
+      <c r="D106" s="11" t="n">
+        <v>2406.888</v>
       </c>
     </row>
     <row r="107" ht="18" customFormat="1" customHeight="1" s="7">
@@ -2014,10 +1896,8 @@
         </is>
       </c>
       <c r="C107" s="20" t="n"/>
-      <c r="D107" s="11" t="inlineStr">
-        <is>
-          <t>2558.744</t>
-        </is>
+      <c r="D107" s="11" t="n">
+        <v>2558.744</v>
       </c>
     </row>
     <row r="108" ht="18" customFormat="1" customHeight="1" s="7">
@@ -2032,10 +1912,8 @@
         </is>
       </c>
       <c r="C108" s="20" t="n"/>
-      <c r="D108" s="11" t="inlineStr">
-        <is>
-          <t>2708.068</t>
-        </is>
+      <c r="D108" s="11" t="n">
+        <v>2708.068</v>
       </c>
     </row>
     <row r="109" ht="18" customFormat="1" customHeight="1" s="7">
@@ -2050,10 +1928,8 @@
         </is>
       </c>
       <c r="C109" s="20" t="n"/>
-      <c r="D109" s="11" t="inlineStr">
-        <is>
-          <t>2961.16</t>
-        </is>
+      <c r="D109" s="11" t="n">
+        <v>2961.16</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1" s="13">
@@ -2068,10 +1944,8 @@
         </is>
       </c>
       <c r="C110" s="20" t="n"/>
-      <c r="D110" s="11" t="inlineStr">
-        <is>
-          <t>2978.875</t>
-        </is>
+      <c r="D110" s="11" t="n">
+        <v>2978.875</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1" s="13">
@@ -2086,10 +1960,8 @@
         </is>
       </c>
       <c r="C111" s="20" t="n"/>
-      <c r="D111" s="11" t="inlineStr">
-        <is>
-          <t>3510.364</t>
-        </is>
+      <c r="D111" s="11" t="n">
+        <v>3510.364</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1" s="13">
@@ -2104,10 +1976,8 @@
         </is>
       </c>
       <c r="C112" s="20" t="n"/>
-      <c r="D112" s="11" t="inlineStr">
-        <is>
-          <t>4155.742</t>
-        </is>
+      <c r="D112" s="11" t="n">
+        <v>4155.742</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1" s="13">
@@ -2122,10 +1992,8 @@
         </is>
       </c>
       <c r="C113" s="20" t="n"/>
-      <c r="D113" s="11" t="inlineStr">
-        <is>
-          <t>4606.245</t>
-        </is>
+      <c r="D113" s="11" t="n">
+        <v>4606.245</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1" s="13">
@@ -2140,10 +2008,8 @@
         </is>
       </c>
       <c r="C114" s="20" t="n"/>
-      <c r="D114" s="11" t="inlineStr">
-        <is>
-          <t>5036.501</t>
-        </is>
+      <c r="D114" s="11" t="n">
+        <v>5036.501</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1" s="13">
@@ -2158,10 +2024,8 @@
         </is>
       </c>
       <c r="C115" s="20" t="n"/>
-      <c r="D115" s="11" t="inlineStr">
-        <is>
-          <t>5560.397</t>
-        </is>
+      <c r="D115" s="11" t="n">
+        <v>5560.397</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1" s="13">
@@ -2176,10 +2040,8 @@
         </is>
       </c>
       <c r="C116" s="20" t="n"/>
-      <c r="D116" s="11" t="inlineStr">
-        <is>
-          <t>6226.021</t>
-        </is>
+      <c r="D116" s="11" t="n">
+        <v>6226.021</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1" s="13">
@@ -2194,10 +2056,8 @@
         </is>
       </c>
       <c r="C117" s="20" t="n"/>
-      <c r="D117" s="11" t="inlineStr">
-        <is>
-          <t>6577.82</t>
-        </is>
+      <c r="D117" s="11" t="n">
+        <v>6577.82</v>
       </c>
     </row>
     <row r="118" ht="19.5" customHeight="1" s="13">
@@ -2212,10 +2072,8 @@
         </is>
       </c>
       <c r="C118" s="20" t="n"/>
-      <c r="D118" s="11" t="inlineStr">
-        <is>
-          <t>7339.619</t>
-        </is>
+      <c r="D118" s="11" t="n">
+        <v>7339.619</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1" s="13">
@@ -2230,92 +2088,90 @@
         </is>
       </c>
       <c r="C119" s="20" t="n"/>
-      <c r="D119" s="11" t="inlineStr">
-        <is>
-          <t>7782.528</t>
-        </is>
+      <c r="D119" s="11" t="n">
+        <v>7782.528</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B115:C115"/>
     <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B108:C108"/>
     <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B106:C106"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B69:C69"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B75:C75"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B73:C73"/>
     <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B93:C93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45219</v>
+        <v>45223</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C72" s="20" t="n"/>
       <c r="D72" s="11" t="n">
-        <v>953.141</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="13">

--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45223</v>
+        <v>45231</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">
@@ -2094,84 +2094,84 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B100:C100"/>
     <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B95:C95"/>
     <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B90:C90"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B75:C75"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B97:C97"/>
     <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B111:C111"/>
     <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B110:C110"/>
     <mergeCell ref="B113:C113"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B93:C93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45231</v>
+        <v>45232</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">

--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45232</v>
+        <v>45234</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">

--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45234</v>
+        <v>45237</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">

--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">
@@ -2094,84 +2094,84 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B115:C115"/>
     <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B108:C108"/>
     <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B106:C106"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B69:C69"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B75:C75"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B73:C73"/>
     <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B93:C93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45238</v>
+        <v>45244</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">

--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45244</v>
+        <v>45253</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">

--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">
@@ -2094,84 +2094,84 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B100:C100"/>
     <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B95:C95"/>
     <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B90:C90"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B75:C75"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B97:C97"/>
     <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B111:C111"/>
     <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B110:C110"/>
     <mergeCell ref="B113:C113"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B93:C93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">

--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -770,7 +770,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" s="13">

--- a/LISTAS/mi/TANQUE.xlsx
+++ b/LISTAS/mi/TANQUE.xlsx
@@ -759,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
     <col width="12.5703125" customWidth="1" style="13" min="1" max="1"/>
@@ -770,9 +770,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45266</v>
-      </c>
-    </row>
+        <v>45264.54810443755</v>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="13">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -795,6 +799,8 @@
       </c>
       <c r="E8" s="16" t="n"/>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="13">
       <c r="A11" s="14" t="inlineStr">
         <is>
@@ -805,6 +811,17 @@
     <row r="12" ht="41.25" customHeight="1" s="13">
       <c r="A12" s="15" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24" ht="33.75" customHeight="1" s="13">
       <c r="B24" s="12" t="inlineStr">
         <is>
@@ -812,6 +829,8 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27" ht="18" customHeight="1" s="13">
       <c r="A27" s="4" t="inlineStr">
         <is>
@@ -843,7 +862,7 @@
       </c>
       <c r="C28" s="20" t="n"/>
       <c r="D28" s="11" t="n">
-        <v>469.482</v>
+        <v>658.89</v>
       </c>
     </row>
     <row r="29" ht="18" customFormat="1" customHeight="1" s="7">
@@ -859,7 +878,7 @@
       </c>
       <c r="C29" s="20" t="n"/>
       <c r="D29" s="11" t="n">
-        <v>536.554</v>
+        <v>753.03</v>
       </c>
     </row>
     <row r="30" ht="18" customFormat="1" customHeight="1" s="7">
@@ -875,7 +894,7 @@
       </c>
       <c r="C30" s="20" t="n"/>
       <c r="D30" s="11" t="n">
-        <v>613.997</v>
+        <v>861.72</v>
       </c>
     </row>
     <row r="31" ht="18" customFormat="1" customHeight="1" s="7">
@@ -891,7 +910,7 @@
       </c>
       <c r="C31" s="20" t="n"/>
       <c r="D31" s="11" t="n">
-        <v>718.271</v>
+        <v>1008.06</v>
       </c>
     </row>
     <row r="32" ht="18" customFormat="1" customHeight="1" s="7">
@@ -907,7 +926,7 @@
       </c>
       <c r="C32" s="20" t="n"/>
       <c r="D32" s="11" t="n">
-        <v>785.847</v>
+        <v>1102.9</v>
       </c>
     </row>
     <row r="33" ht="18" customFormat="1" customHeight="1" s="7">
@@ -923,7 +942,7 @@
       </c>
       <c r="C33" s="20" t="n"/>
       <c r="D33" s="11" t="n">
-        <v>936.438</v>
+        <v>1314.25</v>
       </c>
     </row>
     <row r="34" ht="18" customFormat="1" customHeight="1" s="7">
@@ -939,7 +958,7 @@
       </c>
       <c r="C34" s="20" t="n"/>
       <c r="D34" s="11" t="n">
-        <v>959.213</v>
+        <v>1346.21</v>
       </c>
     </row>
     <row r="35" ht="18" customFormat="1" customHeight="1" s="7">
@@ -955,7 +974,7 @@
       </c>
       <c r="C35" s="20" t="n"/>
       <c r="D35" s="11" t="n">
-        <v>1070.066</v>
+        <v>1501.79</v>
       </c>
     </row>
     <row r="36" ht="18" customFormat="1" customHeight="1" s="7">
@@ -971,7 +990,7 @@
       </c>
       <c r="C36" s="20" t="n"/>
       <c r="D36" s="11" t="n">
-        <v>1295.822</v>
+        <v>1818.63</v>
       </c>
     </row>
     <row r="37" ht="18" customFormat="1" customHeight="1" s="7">
@@ -987,7 +1006,7 @@
       </c>
       <c r="C37" s="20" t="n"/>
       <c r="D37" s="11" t="n">
-        <v>1462.864</v>
+        <v>2053.07</v>
       </c>
     </row>
     <row r="38" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1003,7 +1022,7 @@
       </c>
       <c r="C38" s="20" t="n"/>
       <c r="D38" s="11" t="n">
-        <v>1708.361</v>
+        <v>2397.61</v>
       </c>
     </row>
     <row r="39" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1019,7 +1038,7 @@
       </c>
       <c r="C39" s="20" t="n"/>
       <c r="D39" s="11" t="n">
-        <v>1885.526</v>
+        <v>2646.26</v>
       </c>
     </row>
     <row r="40" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1035,7 +1054,7 @@
       </c>
       <c r="C40" s="20" t="n"/>
       <c r="D40" s="11" t="n">
-        <v>2050.034</v>
+        <v>2877.14</v>
       </c>
     </row>
     <row r="41" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1051,7 +1070,7 @@
       </c>
       <c r="C41" s="20" t="n"/>
       <c r="D41" s="11" t="n">
-        <v>2303.124</v>
+        <v>3232.34</v>
       </c>
     </row>
     <row r="42" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1067,7 +1086,7 @@
       </c>
       <c r="C42" s="20" t="n"/>
       <c r="D42" s="11" t="n">
-        <v>2457.509</v>
+        <v>3449.01</v>
       </c>
     </row>
     <row r="43" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1083,7 +1102,7 @@
       </c>
       <c r="C43" s="20" t="n"/>
       <c r="D43" s="11" t="n">
-        <v>2680.229</v>
+        <v>3761.59</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="13"/>
@@ -1130,7 +1149,7 @@
       </c>
       <c r="C49" s="20" t="n"/>
       <c r="D49" s="11" t="n">
-        <v>1505.89</v>
+        <v>2113.45</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1" s="13">
@@ -1146,7 +1165,7 @@
       </c>
       <c r="C50" s="20" t="n"/>
       <c r="D50" s="11" t="n">
-        <v>1513.482</v>
+        <v>2124.11</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1" s="13">
@@ -1162,7 +1181,7 @@
       </c>
       <c r="C51" s="20" t="n"/>
       <c r="D51" s="11" t="n">
-        <v>1857.684</v>
+        <v>2607.18</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1" s="13">
@@ -1178,7 +1197,7 @@
       </c>
       <c r="C52" s="20" t="n"/>
       <c r="D52" s="11" t="n">
-        <v>1986.763</v>
+        <v>2788.34</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" s="13">
@@ -1194,7 +1213,7 @@
       </c>
       <c r="C53" s="20" t="n"/>
       <c r="D53" s="11" t="n">
-        <v>2116.086</v>
+        <v>2969.84</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" s="13">
@@ -1210,7 +1229,7 @@
       </c>
       <c r="C54" s="20" t="n"/>
       <c r="D54" s="11" t="n">
-        <v>2381.58</v>
+        <v>3342.45</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" s="13">
@@ -1226,7 +1245,7 @@
       </c>
       <c r="C55" s="20" t="n"/>
       <c r="D55" s="11" t="n">
-        <v>2771.34</v>
+        <v>3889.46</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" s="13">
@@ -1242,7 +1261,7 @@
       </c>
       <c r="C56" s="20" t="n"/>
       <c r="D56" s="11" t="n">
-        <v>3102.889</v>
+        <v>4354.78</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1" s="13">
@@ -1258,7 +1277,7 @@
       </c>
       <c r="C57" s="20" t="n"/>
       <c r="D57" s="11" t="n">
-        <v>3548.327</v>
+        <v>4979.93</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" s="13">
@@ -1274,7 +1293,7 @@
       </c>
       <c r="C58" s="20" t="n"/>
       <c r="D58" s="11" t="n">
-        <v>3998.828</v>
+        <v>5612.19</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" s="13">
@@ -1290,7 +1309,7 @@
       </c>
       <c r="C59" s="20" t="n"/>
       <c r="D59" s="11" t="n">
-        <v>4340.497</v>
+        <v>6091.71</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1" s="13">
@@ -1306,7 +1325,7 @@
       </c>
       <c r="C60" s="20" t="n"/>
       <c r="D60" s="11" t="n">
-        <v>4884.644</v>
+        <v>6855.4</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1" s="13">
@@ -1322,7 +1341,7 @@
       </c>
       <c r="C61" s="20" t="n"/>
       <c r="D61" s="11" t="n">
-        <v>5388.291</v>
+        <v>7562.25</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1" s="13">
@@ -1338,9 +1357,11 @@
       </c>
       <c r="C62" s="20" t="n"/>
       <c r="D62" s="11" t="n">
-        <v>5707.184</v>
-      </c>
-    </row>
+        <v>8009.8</v>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64"/>
     <row r="65" ht="33.75" customHeight="1" s="13">
       <c r="B65" s="12" t="inlineStr">
         <is>
@@ -1383,7 +1404,7 @@
       </c>
       <c r="C68" s="20" t="n"/>
       <c r="D68" s="11" t="n">
-        <v>607.671</v>
+        <v>852.84</v>
       </c>
     </row>
     <row r="69" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1399,7 +1420,7 @@
       </c>
       <c r="C69" s="20" t="n"/>
       <c r="D69" s="11" t="n">
-        <v>625.134</v>
+        <v>877.35</v>
       </c>
     </row>
     <row r="70" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1415,7 +1436,7 @@
       </c>
       <c r="C70" s="20" t="n"/>
       <c r="D70" s="11" t="n">
-        <v>707.388</v>
+        <v>992.79</v>
       </c>
     </row>
     <row r="71" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1431,7 +1452,7 @@
       </c>
       <c r="C71" s="20" t="n"/>
       <c r="D71" s="11" t="n">
-        <v>824.064</v>
+        <v>1156.54</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1" s="13">
@@ -1447,7 +1468,7 @@
       </c>
       <c r="C72" s="20" t="n"/>
       <c r="D72" s="11" t="n">
-        <v>100</v>
+        <v>1337.69</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="13">
@@ -1463,7 +1484,7 @@
       </c>
       <c r="C73" s="20" t="n"/>
       <c r="D73" s="11" t="n">
-        <v>1104.993</v>
+        <v>1550.81</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1" s="13">
@@ -1479,7 +1500,7 @@
       </c>
       <c r="C74" s="20" t="n"/>
       <c r="D74" s="11" t="n">
-        <v>1237.612</v>
+        <v>1736.93</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="13">
@@ -1495,7 +1516,7 @@
       </c>
       <c r="C75" s="20" t="n"/>
       <c r="D75" s="11" t="n">
-        <v>1311.008</v>
+        <v>1839.94</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" s="13">
@@ -1511,7 +1532,7 @@
       </c>
       <c r="C76" s="20" t="n"/>
       <c r="D76" s="11" t="n">
-        <v>1543.85</v>
+        <v>2166.73</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1" s="13">
@@ -1527,7 +1548,7 @@
       </c>
       <c r="C77" s="20" t="n"/>
       <c r="D77" s="11" t="n">
-        <v>1789.351</v>
+        <v>2511.28</v>
       </c>
     </row>
     <row r="78" ht="18.75" customHeight="1" s="13">
@@ -1543,7 +1564,7 @@
       </c>
       <c r="C78" s="20" t="n"/>
       <c r="D78" s="11" t="n">
-        <v>1993.592</v>
+        <v>2797.92</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1" s="13">
@@ -1559,7 +1580,7 @@
       </c>
       <c r="C79" s="20" t="n"/>
       <c r="D79" s="11" t="n">
-        <v>2234.28</v>
+        <v>3135.72</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1" s="13">
@@ -1575,7 +1596,7 @@
       </c>
       <c r="C80" s="20" t="n"/>
       <c r="D80" s="11" t="n">
-        <v>2492.942</v>
+        <v>3498.74</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1" s="13">
@@ -1591,7 +1612,7 @@
       </c>
       <c r="C81" s="20" t="n"/>
       <c r="D81" s="11" t="n">
-        <v>2640.49</v>
+        <v>3705.82</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1" s="13">
@@ -1607,7 +1628,7 @@
       </c>
       <c r="C82" s="20" t="n"/>
       <c r="D82" s="11" t="n">
-        <v>2862.453</v>
+        <v>4017.33</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1" s="13">
@@ -1623,9 +1644,11 @@
       </c>
       <c r="C83" s="20" t="n"/>
       <c r="D83" s="11" t="n">
-        <v>3125.665</v>
-      </c>
-    </row>
+        <v>4386.74</v>
+      </c>
+    </row>
+    <row r="84"/>
+    <row r="85"/>
     <row r="86" ht="33.75" customHeight="1" s="13">
       <c r="B86" s="12" t="inlineStr">
         <is>
@@ -1633,6 +1656,7 @@
         </is>
       </c>
     </row>
+    <row r="87"/>
     <row r="88" ht="18" customHeight="1" s="13">
       <c r="A88" s="4" t="inlineStr">
         <is>
@@ -1664,7 +1688,7 @@
       </c>
       <c r="C89" s="20" t="n"/>
       <c r="D89" s="11" t="n">
-        <v>259.878</v>
+        <v>364.72</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1" s="13">
@@ -1680,7 +1704,7 @@
       </c>
       <c r="C90" s="20" t="n"/>
       <c r="D90" s="11" t="n">
-        <v>312.062</v>
+        <v>437.96</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1" s="13">
@@ -1696,7 +1720,7 @@
       </c>
       <c r="C91" s="20" t="n"/>
       <c r="D91" s="11" t="n">
-        <v>337.37</v>
+        <v>473.48</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1" s="13">
@@ -1712,7 +1736,7 @@
       </c>
       <c r="C92" s="20" t="n"/>
       <c r="D92" s="11" t="n">
-        <v>418.61</v>
+        <v>587.5</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1" s="13">
@@ -1728,7 +1752,7 @@
       </c>
       <c r="C93" s="20" t="n"/>
       <c r="D93" s="11" t="n">
-        <v>456.827</v>
+        <v>641.13</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1" s="13">
@@ -1744,7 +1768,7 @@
       </c>
       <c r="C94" s="20" t="n"/>
       <c r="D94" s="11" t="n">
-        <v>492.008</v>
+        <v>690.51</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1" s="13">
@@ -1760,7 +1784,7 @@
       </c>
       <c r="C95" s="20" t="n"/>
       <c r="D95" s="11" t="n">
-        <v>539.842</v>
+        <v>757.64</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1" s="13">
@@ -1776,7 +1800,7 @@
       </c>
       <c r="C96" s="20" t="n"/>
       <c r="D96" s="11" t="n">
-        <v>688.913</v>
+        <v>966.86</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1" s="13">
@@ -1792,7 +1816,7 @@
       </c>
       <c r="C97" s="20" t="n"/>
       <c r="D97" s="11" t="n">
-        <v>749.146</v>
+        <v>1051.39</v>
       </c>
     </row>
     <row r="98" ht="19.5" customHeight="1" s="13">
@@ -1808,7 +1832,7 @@
       </c>
       <c r="C98" s="20" t="n"/>
       <c r="D98" s="11" t="n">
-        <v>878.223</v>
+        <v>1232.55</v>
       </c>
     </row>
     <row r="99" ht="17.25" customHeight="1" s="13">
@@ -1824,7 +1848,7 @@
       </c>
       <c r="C99" s="20" t="n"/>
       <c r="D99" s="11" t="n">
-        <v>992.114</v>
+        <v>1392.39</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1" s="13">
@@ -1840,9 +1864,11 @@
       </c>
       <c r="C100" s="20" t="n"/>
       <c r="D100" s="11" t="n">
-        <v>1068.042</v>
-      </c>
-    </row>
+        <v>1498.95</v>
+      </c>
+    </row>
+    <row r="101"/>
+    <row r="102"/>
     <row r="103" ht="33.75" customHeight="1" s="13">
       <c r="B103" s="12" t="inlineStr">
         <is>
@@ -1850,6 +1876,7 @@
         </is>
       </c>
     </row>
+    <row r="104"/>
     <row r="105" ht="18" customHeight="1" s="13">
       <c r="A105" s="4" t="inlineStr">
         <is>
@@ -1881,7 +1908,7 @@
       </c>
       <c r="C106" s="20" t="n"/>
       <c r="D106" s="11" t="n">
-        <v>2406.888</v>
+        <v>3377.97</v>
       </c>
     </row>
     <row r="107" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1897,7 +1924,7 @@
       </c>
       <c r="C107" s="20" t="n"/>
       <c r="D107" s="11" t="n">
-        <v>2558.744</v>
+        <v>3591.09</v>
       </c>
     </row>
     <row r="108" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1913,7 +1940,7 @@
       </c>
       <c r="C108" s="20" t="n"/>
       <c r="D108" s="11" t="n">
-        <v>2708.068</v>
+        <v>3800.66</v>
       </c>
     </row>
     <row r="109" ht="18" customFormat="1" customHeight="1" s="7">
@@ -1929,7 +1956,7 @@
       </c>
       <c r="C109" s="20" t="n"/>
       <c r="D109" s="11" t="n">
-        <v>2961.16</v>
+        <v>4155.87</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1" s="13">
@@ -1945,7 +1972,7 @@
       </c>
       <c r="C110" s="20" t="n"/>
       <c r="D110" s="11" t="n">
-        <v>2978.875</v>
+        <v>4180.73</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1" s="13">
@@ -1961,7 +1988,7 @@
       </c>
       <c r="C111" s="20" t="n"/>
       <c r="D111" s="11" t="n">
-        <v>3510.364</v>
+        <v>4926.65</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1" s="13">
@@ -1977,7 +2004,7 @@
       </c>
       <c r="C112" s="20" t="n"/>
       <c r="D112" s="11" t="n">
-        <v>4155.742</v>
+        <v>5832.41</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1" s="13">
@@ -1993,7 +2020,7 @@
       </c>
       <c r="C113" s="20" t="n"/>
       <c r="D113" s="11" t="n">
-        <v>4606.245</v>
+        <v>6464.68</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1" s="13">
@@ -2009,7 +2036,7 @@
       </c>
       <c r="C114" s="20" t="n"/>
       <c r="D114" s="11" t="n">
-        <v>5036.501</v>
+        <v>7068.52</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1" s="13">
@@ -2025,7 +2052,7 @@
       </c>
       <c r="C115" s="20" t="n"/>
       <c r="D115" s="11" t="n">
-        <v>5560.397</v>
+        <v>7803.79</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1" s="13">
@@ -2041,7 +2068,7 @@
       </c>
       <c r="C116" s="20" t="n"/>
       <c r="D116" s="11" t="n">
-        <v>6226.021</v>
+        <v>8737.969999999999</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1" s="13">
@@ -2057,7 +2084,7 @@
       </c>
       <c r="C117" s="20" t="n"/>
       <c r="D117" s="11" t="n">
-        <v>6577.82</v>
+        <v>9231.700000000001</v>
       </c>
     </row>
     <row r="118" ht="19.5" customHeight="1" s="13">
@@ -2073,7 +2100,7 @@
       </c>
       <c r="C118" s="20" t="n"/>
       <c r="D118" s="11" t="n">
-        <v>7339.619</v>
+        <v>10300.86</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1" s="13">
@@ -2089,89 +2116,90 @@
       </c>
       <c r="C119" s="20" t="n"/>
       <c r="D119" s="11" t="n">
-        <v>7782.528</v>
-      </c>
-    </row>
+        <v>10922.46</v>
+      </c>
+    </row>
+    <row r="120"/>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
     <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B106:C106"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B71:C71"/>
     <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B111:C111"/>
     <mergeCell ref="B73:C73"/>
     <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
     <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
     <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B113:C113"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
